--- a/TIME TABLE SAMPLE DATA/shared-classes-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/shared-classes-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajas\OneDrive\Desktop\Timetable\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_2B59D2BFD3705AEF40637A13413088B352998C64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{301F993E-97BC-4791-985A-6C446FDD721E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485ECA5E-2342-4FF0-9467-4A46CCB6C4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>year</t>
   </si>
@@ -31,16 +31,10 @@
     <t>subject</t>
   </si>
   <si>
-    <t>2nd Year</t>
+    <t>C4,C5</t>
   </si>
   <si>
-    <t>C2, C3</t>
-  </si>
-  <si>
-    <t>C4, C5</t>
-  </si>
-  <si>
-    <t>TECHNICAL</t>
+    <t>3rd Year</t>
   </si>
 </sst>
 </file>
@@ -419,24 +413,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
+      <c r="C2">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
+      <c r="C3">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/TIME TABLE SAMPLE DATA/shared-classes-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/shared-classes-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajas\OneDrive\Desktop\Timetable\TIME TABLE SAMPLE DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485ECA5E-2342-4FF0-9467-4A46CCB6C4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EC438D-C26F-4485-B633-AE256961BA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>year</t>
   </si>
@@ -31,10 +31,10 @@
     <t>subject</t>
   </si>
   <si>
-    <t>C4,C5</t>
+    <t>3rd Year</t>
   </si>
   <si>
-    <t>3rd Year</t>
+    <t>C3,C5</t>
   </si>
 </sst>
 </file>
@@ -397,10 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -411,26 +411,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
       <c r="C2">
         <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/TIME TABLE SAMPLE DATA/shared-classes-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/shared-classes-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajas\OneDrive\Desktop\Timetable\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EC438D-C26F-4485-B633-AE256961BA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD6E2CF-CDDF-41DF-8D10-D593DEA37F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>year</t>
   </si>
@@ -29,12 +29,6 @@
   </si>
   <si>
     <t>subject</t>
-  </si>
-  <si>
-    <t>3rd Year</t>
-  </si>
-  <si>
-    <t>C3,C5</t>
   </si>
 </sst>
 </file>
@@ -397,10 +391,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -411,17 +405,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
